--- a/outputs/metrics/sequence_window_test_metrics.xlsx
+++ b/outputs/metrics/sequence_window_test_metrics.xlsx
@@ -485,34 +485,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.6563517915309446</v>
+        <v>0.6791530944625407</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3498098859315589</v>
+        <v>0.532319391634981</v>
       </c>
       <c r="C2" t="n">
-        <v>0.303030303030303</v>
+        <v>0.3457943925233645</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4658227848101266</v>
+        <v>0.5870020964360587</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3036303630363036</v>
+        <v>0.4154302670623146</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7390075070683435</v>
+        <v>0.7480636530066187</v>
       </c>
       <c r="G2" t="n">
-        <v>311</v>
+        <v>277</v>
       </c>
       <c r="H2" t="n">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="I2" t="n">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="J2" t="n">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="K2" t="n">
         <v>0.5</v>
@@ -530,34 +530,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.6954397394136808</v>
+        <v>0.6938110749185668</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7946768060836502</v>
+        <v>0.6349809885931559</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.3552123552123552</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6909090909090909</v>
+        <v>0.6398467432950191</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5277777777777778</v>
+        <v>0.4704225352112676</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7664034318026712</v>
+        <v>0.7607704223673805</v>
       </c>
       <c r="G3" t="n">
-        <v>218</v>
+        <v>259</v>
       </c>
       <c r="H3" t="n">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="I3" t="n">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="J3" t="n">
-        <v>209</v>
+        <v>167</v>
       </c>
       <c r="K3" t="n">
         <v>0.5</v>
@@ -575,34 +575,34 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.6563517915309446</v>
+        <v>0.6824104234527687</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6920152091254753</v>
+        <v>0.6121673003802282</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.3661417322834646</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6330434782608696</v>
+        <v>0.6228239845261122</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4631043256997455</v>
+        <v>0.4522471910112359</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7212635273471776</v>
+        <v>0.737490927604996</v>
       </c>
       <c r="G4" t="n">
-        <v>221</v>
+        <v>258</v>
       </c>
       <c r="H4" t="n">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="I4" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="J4" t="n">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="K4" t="n">
         <v>0.5</v>
@@ -620,34 +620,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.7052117263843648</v>
+        <v>0.7019543973941368</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5893536121673004</v>
+        <v>0.623574144486692</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3201754385964912</v>
+        <v>0.3387096774193548</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6313645621181263</v>
+        <v>0.6418786692759295</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4613095238095238</v>
+        <v>0.4726224783861672</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7620270167798686</v>
+        <v>0.761409552284077</v>
       </c>
       <c r="G5" t="n">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="H5" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="I5" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="J5" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="K5" t="n">
         <v>0.5</v>
@@ -665,34 +665,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.6872964169381107</v>
+        <v>0.6074918566775245</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8174904942965779</v>
+        <v>0.8973384030418251</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4011142061281337</v>
+        <v>0.4755555555555556</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6913183279742765</v>
+        <v>0.6619915848527349</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5282555282555282</v>
+        <v>0.4947589098532495</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7423114837563507</v>
+        <v>0.7436330744315535</v>
       </c>
       <c r="G6" t="n">
-        <v>207</v>
+        <v>137</v>
       </c>
       <c r="H6" t="n">
-        <v>144</v>
+        <v>214</v>
       </c>
       <c r="I6" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="J6" t="n">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="K6" t="n">
         <v>0.5</v>
@@ -710,34 +710,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.6954397394136808</v>
+        <v>0.6986970684039088</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7642585551330798</v>
+        <v>0.7338403041825095</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3834355828220859</v>
+        <v>0.3733766233766234</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6825127334465195</v>
+        <v>0.6760070052539404</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5180412371134021</v>
+        <v>0.5105820105820106</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7716572963721253</v>
+        <v>0.7621570093052983</v>
       </c>
       <c r="G7" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="H7" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="I7" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="J7" t="n">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="K7" t="n">
         <v>0.5</v>
